--- a/Lenguaje/NormalUse.xlsx
+++ b/Lenguaje/NormalUse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/zyyeche_upv_edu_es/Documents/Thalassar/Colangs/Lenguaje/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_AD4D2F04E46CFB4ACB3E20196D56F008693EDF13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E01139A-9D69-4AFF-B82E-5E8631CF58F8}"/>
+  <xr:revisionPtr revIDLastSave="211" documentId="11_AD4D2F04E46CFB4ACB3E20196D56F008693EDF13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{160B44AD-2678-45B4-9903-7BE8431EB480}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="150">
   <si>
     <t>橄榄</t>
   </si>
@@ -222,6 +222,346 @@
   </si>
   <si>
     <t>自然概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Olivo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Der</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Olivos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Die</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aquamaln</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aquamalnen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>葡萄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ösun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cepa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cepas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Padada</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Padadas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Porro Larju</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Porros Larjus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Colscha</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Colschas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Das</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sativa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sativas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rrapa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rrapas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pasnaiya</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pasnaiyas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robeles</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Schienhait</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cesirali</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cesiralis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jaha</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jahas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kukunus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kukunu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agupaña</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agupañas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Örsu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Örsus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polén</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polenes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kún</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kunes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maicth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芜菁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cituru/Pituru</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Apfel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Birne</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cereza</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cerezas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Birnes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Apfeles</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咖啡豆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kaffee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>萝卜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苹果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梨子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豆子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘑菇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防风草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昙花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kafes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山楂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pinati</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pinatis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epiphillo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epiphillos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meikes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Joya</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Joyas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fixa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fixas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fragne</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fragnes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flures</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Citurus/Piturus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>橙子/橘子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duocth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -370,6 +710,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCA12AF1-EA08-48BE-B31B-8907C3EE36B5}" name="Tabla1" displayName="Tabla1" ref="F5:I44" totalsRowShown="0">
+  <autoFilter ref="F5:I44" xr:uid="{DCA12AF1-EA08-48BE-B31B-8907C3EE36B5}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{17EDDDAA-211F-4FAF-BA45-93C07B94607C}" name="名称"/>
+    <tableColumn id="2" xr3:uid="{5A43E15F-7E4C-4F6B-AC72-9E03C339D278}" name="Gender"/>
+    <tableColumn id="3" xr3:uid="{A31A725B-4F15-4599-A7C5-9E6181F38A50}" name="Cr"/>
+    <tableColumn id="4" xr3:uid="{EA8609EE-C5EF-4BF6-9439-F38094EC4E6B}" name="复数"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -635,15 +992,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="25.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.75" style="9" customWidth="1"/>
     <col min="2" max="2" width="3.25" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="16.75" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="5" width="2.5" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +1014,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -659,7 +1022,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -667,227 +1030,662 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
+        <v>148</v>
+      </c>
+      <c r="G28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" t="s">
+        <v>112</v>
+      </c>
+      <c r="I28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s">
+        <v>113</v>
+      </c>
+      <c r="I29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" t="s">
+        <v>70</v>
+      </c>
+      <c r="H32" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" t="s">
+        <v>135</v>
+      </c>
+      <c r="I33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s">
+        <v>137</v>
+      </c>
+      <c r="I34" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F35" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" t="s">
+        <v>139</v>
+      </c>
+      <c r="I35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F36" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" t="s">
+        <v>70</v>
+      </c>
+      <c r="H36" t="s">
+        <v>141</v>
+      </c>
+      <c r="I36" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
+        <v>119</v>
+      </c>
+      <c r="G38" t="s">
+        <v>70</v>
+      </c>
+      <c r="H38" t="s">
+        <v>120</v>
+      </c>
+      <c r="I38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F39" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>37</v>
+      </c>
+      <c r="G42" t="s">
+        <v>70</v>
+      </c>
+      <c r="H42" t="s">
+        <v>145</v>
+      </c>
+      <c r="I42" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G44" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>47</v>
       </c>
@@ -932,7 +1730,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>56</v>
       </c>
@@ -965,5 +1763,9 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>